--- a/kariwala-connect-seed.xlsx
+++ b/kariwala-connect-seed.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -436,6 +436,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +475,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LogoURL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +515,11 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>Oneness of Thoughts, Words and Actions — Kariwala's annual meeting.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>icons/aikyam-logo.png</t>
         </is>
       </c>
     </row>
@@ -523,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -531,6 +542,8 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -559,6 +572,16 @@
           <t>Speaker</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>FileURL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>FileTitle</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -581,7 +604,6 @@
           <t>Assemble and lighting of Diya</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -636,6 +658,16 @@
           <t>Anand, Ranjit and Manish</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/PASTE_FILE_ID/view</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Balanced Scorecard.pptx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -658,7 +690,6 @@
           <t>Tea Break</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -735,7 +766,6 @@
           <t>Lunch</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -812,7 +842,6 @@
           <t>Tea Break + Games</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -862,7 +891,6 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -912,7 +940,6 @@
           <t>Breakfast</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +962,6 @@
           <t>Recap of Day 1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -985,7 +1011,6 @@
           <t>Tea Break</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1035,7 +1060,6 @@
           <t>Working Lunch</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1085,7 +1109,6 @@
           <t>Conclusion and Takeaways</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1108,7 +1131,6 @@
           <t>High Tea</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1160,7 +1182,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Example: Balanced Scorecard.pptx</t>
+          <t>Full Agenda.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1170,7 +1192,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Presentation</t>
+          <t>PDF</t>
         </is>
       </c>
     </row>
